--- a/raw csv data for gcamdata_gcam-china (gcam-china v8 HK annotated).xlsx
+++ b/raw csv data for gcamdata_gcam-china (gcam-china v8 HK annotated).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\0_HKU_work\2_GCAM\GCAM_china\gcam-hk-v8-Windows-Release-Package\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D79AB90-1777-4BA5-AC5B-2207D17DFB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82B4502-AF88-42E7-A5F5-56AD306B7C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,8 +23,19 @@
     <sheet name="List - climate region" sheetId="8" r:id="rId8"/>
     <sheet name="List - grid region" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -33,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="1318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2894" uniqueCount="1330">
   <si>
     <t>FileName</t>
   </si>
@@ -1843,9 +1854,6 @@
     <t>PNNL's research based on Dahowski et al. (2010, 2017)</t>
   </si>
   <si>
-    <t>copy GD，参照数据含义确定（参考 HKData/CCS/）</t>
-  </si>
-  <si>
     <t>province.name,ID,CO2_Mt,Cost_2005USDtCO2</t>
   </si>
   <si>
@@ -2016,9 +2024,6 @@
     <t>Bob Dahowski and Casie Davidson - PNNL</t>
   </si>
   <si>
-    <t>copy GD, maxResource设为0，依据为Yiming Wei 2022 Figure 1b 以及 Discussion 倒数第二段说到 CCUS is not suitable for South China regions like Guangdong ("GD") because they are "far from onshore storage sites".</t>
-  </si>
-  <si>
     <t>cnnnc</t>
   </si>
   <si>
@@ -2051,12 +2056,6 @@
     <t>China power statistical yearbook</t>
   </si>
   <si>
-    <t>（HKData/energybalance/power system (fuel mix) CPSY_GWh_province_F_elec_out HK 100GWh.csv
-2000年开始https://www.iea.org/countries/hong-kong/electricity和https://www.emsd.gov.hk/energyland/en/energy/energy_use/energy_scene.html
-2000年之前  香港能源统计年鉴 https://www.ceicdata.com/zh-hans/hong-kong/energy-production-and-consumption/hk-electricity-production-from-coal-sources--of-total 和 https://www.sciencedirect.com/science/article/pii/S0301421500000690#aep-section-id9
-非可再生能源发电量使用香港能源统计年鉴中的发电量数据进行校准</t>
-  </si>
-  <si>
     <t>cinnnnnnnnnnni</t>
   </si>
   <si>
@@ -2156,9 +2155,6 @@
     <t>steel and coke production are from the China Statistical Yearbook. Other energy consumption is from the MEIC-HR Emissions Inventory facility-level energy consumption data summed at the provincial level.</t>
   </si>
   <si>
-    <t>在提取处理 IEA_EnergyBalance_2019 的过程中估计的数据，大部分 energy.input 和 production 为 0（只涉及1975,1990等模型校准年）(HKData/energybalance/Extract and Process IEA PREBUILT_DATA/processed_data/detail_industry_energyuse)</t>
-  </si>
-  <si>
     <t>cncccn</t>
   </si>
   <si>
@@ -2351,10 +2347,6 @@
     <t>China statistical yearbook via LBL China Energy Databook v8</t>
   </si>
   <si>
-    <t>- 待更新
-1971-2011</t>
-  </si>
-  <si>
     <t>ciccn</t>
   </si>
   <si>
@@ -2385,10 +2377,6 @@
   </si>
   <si>
     <t>China statistical yearbook via LBL China Energy Databook v9(before 2014, 2015 data is same with 2014),2021 data from China Energy Statistical Yearbook</t>
-  </si>
-  <si>
-    <t>从 IEA_EnergyBalance_2019 中提取并处理得到香港的数据en_balance_Mtce_Yh_HK
-(HKData/energybalance/Extract and Process IEA PREBUILT_DATA/processed_data)</t>
   </si>
   <si>
     <t>province.name,year,EBMaterial,EBProcess,value</t>
@@ -3249,10 +3237,6 @@
     <t>37,RusCstSE,HL,1975,0.013882249,0.021851954,0.004270594,0.02421592,0.001538968</t>
   </si>
   <si>
-    <t>ZH: 气候/度日数据。用于 GCAM-China gcamdata 中的 Volume of water withdrawals at individual basin-province combinations for 2010 as calucated from Khan et al. (2023) data and other years from Huang et al. (2018)；字段包括 GCAM_basin_ID,basin_name,state_abbr,year,Domestic,Electricity,Livestock,Manufacturing,Mining。本地说明：NA
-EN: climate dataset for GCAM-China gcamdata: Volume of water withdrawals at individual basin-province combinations for 2010 as calucated from Khan et al. (2023) data and other years from Huang et al. (2018). Columns: GCAM_basin_ID,basin_name,state_abbr,year,Domestic,Electricity,Livestock,Manufacturing,Mining; local note: NA</t>
-  </si>
-  <si>
     <t>nuc_share_weight_assumptions_high</t>
   </si>
   <si>
@@ -3461,10 +3445,6 @@
   </si>
   <si>
     <t>https://github.com/JGCRI/pridr   24/08/2025 xsl copy 2020 to 2021, China Statistical Yearbook</t>
-  </si>
-  <si>
-    <t>Hong Kong's urban data is collected from Rao et al (SSPs seq(2020, 2100, 5) and computed from pridr package's Input_Data、compute_deciles_lognormal function (Historical, 2011:2015)，并设 resid_rural 的share 为 0
-具体见 ./HKData/scioeco/decile of gdp per capita (SSPs Gini GDP Pop)/</t>
   </si>
   <si>
     <t>ccicnccnnn</t>
@@ -3596,9 +3576,6 @@
     <t>Refined liquids source: LBL 2014 China Key Energy Statistics price cap on diesel, Gas source: NDRC http://www.ndrc.gov.cn/zcfb/zcfbtz/201502/t20150228_665694.html accessed 10/14/2015, Coal Source: from http://www.coal-link.com/coal/list/79/ accessed 4/9/2015"</t>
   </si>
   <si>
-    <t>香港能源统计年鉴中 2015 油产品和煤产品进口价格（需要转换单位）</t>
-  </si>
-  <si>
     <t>province.name,coal,refined.liquids,gas</t>
   </si>
   <si>
@@ -3625,9 +3602,6 @@
     <t>He and Kammen 2016</t>
   </si>
   <si>
-    <t>原始研究无香港，参考Cooperative Planning of Renewable Generations for Interconnected Microgrids（https://doi.org/10.1109/TSG.2016.2552642）Figure 1</t>
-  </si>
-  <si>
     <t>cnn</t>
   </si>
   <si>
@@ -3660,9 +3634,6 @@
     <t>Provincial-level supply curves are generated by Shen and Yin</t>
   </si>
   <si>
-    <t>原始研究无香港,参考 http://www.lsgi.polyu.edu.hk/rsl/lsw/solarenergyHK/Results.html 设置 maxResource</t>
-  </si>
-  <si>
     <t>province.name,maxResource,mid.price,curve.exponent,renewresource</t>
   </si>
   <si>
@@ -3953,9 +3924,6 @@
     <t>Wind power potential and base costs by province</t>
   </si>
   <si>
-    <t>原始研究无香港,copy GD，参考Analysis of Hong Kong’s Wind Energy: Power Potential, Development Constraints, and Experiences from Other Countries for Local Wind Energy Promotion Strategies（https://doi.org/10.3390/su11030924）设置maxResource 和mid.price</t>
-  </si>
-  <si>
     <t>province.name,maxResource,mid.price,curve.exponent,base.cost</t>
   </si>
   <si>
@@ -4259,13 +4227,91 @@
   <si>
     <t>average living space per person:《Housing in Figures 2023》有2013(13㎡)2018(13.3㎡)2023(13.8㎡)的值,《Housing in Figures 2013》有2003(11.3㎡)2008(12.4㎡)2013(13㎡)的值 …但是根据《香港2030+》，2021年16m2，2016年15m2
 2000年起有数据，之前的靠猜</t>
+  </si>
+  <si>
+    <t>copy Hainan，参照数据含义确定（参考 HKData/CCS/）</t>
+  </si>
+  <si>
+    <t>加上香港</t>
+  </si>
+  <si>
+    <t>原数据包含香港澳门（原数据列出了所有的省份）</t>
+  </si>
+  <si>
+    <t>copy Hainan, maxResource设为0，依据为Yiming Wei 2022 Figure 1b 以及 Discussion 倒数第二段说到 CCUS is not suitable for South China regions like Guangdong ("GD") because they are "far from onshore storage sites".</t>
+  </si>
+  <si>
+    <t>（HKData/energybalance/power system (fuel mix) CPSY_GWh_province_F_elec_out HK 100GWh.csv
+2000年开始https://www.iea.org/countries/hong-kong/electricity和https://www.emsd.gov.hk/energyland/en/energy/energy_use/energy_scene.html
+2000年之前  香港能源统计年鉴 https://www.ceicdata.com/zh-hans/hong-kong/energy-production-and-consumption/hk-electricity-production-from-coal-sources--of-total 和 https://www.sciencedirect.com/science/article/pii/S0301421500000690#aep-section-id9
+非可再生能源发电量使用香港能源统计年鉴中的发电量数据进行校准。需要注意的是，coal 对应的其实是中国电力年鉴中的“火电”，包含了燃煤燃气燃油</t>
+  </si>
+  <si>
+    <t>根据ChatGPT的建议，结合GD、HI：香港主要的热电厂为沿海电厂，基于海水冷却</t>
+  </si>
+  <si>
+    <t>在提取处理 IEA_EnergyBalance_2023 的过程中估计的数据，大部分 energy.input 和 production 为 0（只涉及1975,1990等模型校准年）(HKData/energybalance/Extract and Process IEA PREBUILT_DATA/processed_data/detail_industry_energyuse)</t>
+  </si>
+  <si>
+    <t>从 IEA_EnergyBalance_2023 中提取并处理得到香港的数据en_balance_Mtce_Yh_HK
+(HKData/energybalance/Extract and Process IEA PREBUILT_DATA/processed_data)</t>
+  </si>
+  <si>
+    <t>香港从 1997 年后不再新建燃煤机组。根据 ChatGPT 和其他信息合理推断。2021 年的燃煤发电量由哪些机组share</t>
+  </si>
+  <si>
+    <t>在提取处理 IEA_EnergyBalance_2019 的过程中估计的数据，大部分 energy.input 和 production 为 0（只涉及1975,1990等模型校准年）(HKData/energybalance/Extract and Process IEA PREBUILT_DATA/processed_data/detail_industry_energyuse)。经过ChatGPT汇总信息并估计</t>
+  </si>
+  <si>
+    <t>参考浙江，香港没有初级能源mining生产，所以share全部设置为0</t>
+  </si>
+  <si>
+    <t>水资源数据系统中用于 primary energy mining 的水源分配表。它不是水量数据，也不是采矿产量数据，而是一组 无量纲 share 参数</t>
+  </si>
+  <si>
+    <t>在每个 GCAM basin × 省份 组合中，不同非灌溉部门的取水量，单位为 km³。生活、电力、畜牧、制造业、采矿部门取水</t>
+  </si>
+  <si>
+    <t>参考广东省灌溉取水流域，香港仅东江流域，因此仅涉及 basin-ChinaCst（沿海），根据ChatGPT分析，对香港设置极小正值</t>
+  </si>
+  <si>
+    <t>赋值极小正值 0.00000002(1990)~0.0000001(2021)</t>
+  </si>
+  <si>
+    <t>香港能源统计年鉴中 2015 油产品和煤产品进口价格（需要转换单位）：煤价格换算采用 2015 年平均汇率 1 CNY = 1.2341 HKD所以香港 447 HKD/t ≈ 447 / 1.2341 = 362.2 RMB/t 。柴油产品 4052，天然气 2855 ------------ 不按这个来：
+Hong Kong,406.77 coal,8036 refined liquids,2860 gas</t>
+  </si>
+  <si>
+    <t>Hong Kong's urban data is collected from Rao et al (SSPs seq(2020, 2100, 5) and computed from pridr package's Input_Data、compute_deciles_lognormal function (Historical, 2011:2015)，并设 resid_rural 的share 为 0
+具体见 ./HKData/scioeco/decile of gdp per capita (SSPs Gini GDP Pop)/。与 v7 一样，仅将 v7 中的年份 2020 改为了 2021</t>
+  </si>
+  <si>
+    <t>中国总量，加上香港的量≈原中国总量乘以100.001%</t>
+  </si>
+  <si>
+    <t>https://ssp.apps.ece.iiasa.ac.at/basic-drivers?type=line-chart&amp;regions=97 使用香港的人口预测换算增长率</t>
+  </si>
+  <si>
+    <t>https://ssp.apps.ece.iiasa.ac.at/basic-drivers?type=line-chart&amp;regions=97  使用香港的GDP预测换算增长率</t>
+  </si>
+  <si>
+    <t>基于香港的用水数据分配和估算。其中电力系统用水通过 Domestic × 广东同年 Electricity / Domestic 比例 × scaling factor 来估计，先用 scaling factor = 0.5，如果数据离谱，再用 scaling factor = 0.3~0.75 代替。Mining 赋值极小正值 0.000000001，避免香港没有 water_td_pri_C water_td_pri_W</t>
+  </si>
+  <si>
+    <t>原始研究无香港,参考 http://www.lsgi.polyu.edu.hk/rsl/lsw/solarenergyHK/Results.html 等信息，ChatGPT 合理估算。见 HKData/solarwind/solar pv potential curve</t>
+  </si>
+  <si>
+    <t>原始研究无香港，参考Cooperative Planning of Renewable Generations for Interconnected Microgrids（https://doi.org/10.1109/TSG.2016.2552642）Figure 1和ChatGPT 合理估算</t>
+  </si>
+  <si>
+    <t>原始研究无香港,copy GD，参考Analysis of Hong Kong’s Wind Energy: Power Potential, Development Constraints, and Experiences from Other Countries for Local Wind Energy Promotion Strategies（https://doi.org/10.3390/su11030924）设置maxResource 和mid.price，以及 ChatGPT合理估算。见 HKData/solarwind/onshore wind potential curve and capacity factor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -4274,6 +4320,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -4314,10 +4366,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -4331,8 +4384,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4652,7 +4709,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>1316</v>
+        <v>1304</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>26</v>
@@ -8154,16 +8211,16 @@
         <v>567</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>568</v>
+        <v>1306</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>83</v>
       </c>
       <c r="H76" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="I76" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
@@ -8173,7 +8230,7 @@
         <v>550</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2" t="s">
@@ -8183,10 +8240,10 @@
         <v>40</v>
       </c>
       <c r="Q76" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="R76" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="R76" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="S76" s="2" t="s">
         <v>224</v>
@@ -8194,40 +8251,40 @@
     </row>
     <row r="77" spans="1:19" ht="171">
       <c r="A77" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="F77" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="F77" s="2" t="s">
+      <c r="G77" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="H77" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="H77" s="2" t="s">
+      <c r="I77" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="I77" s="2" t="s">
+      <c r="J77" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="J77" s="2" t="s">
+      <c r="K77" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="K77" s="2" t="s">
+      <c r="L77" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -8235,13 +8292,13 @@
         <v>26</v>
       </c>
       <c r="P77" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="Q77" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="Q77" s="2" t="s">
+      <c r="R77" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="R77" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>188</v>
@@ -8249,13 +8306,13 @@
     </row>
     <row r="78" spans="1:19" ht="99.75">
       <c r="A78" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>591</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
@@ -8264,10 +8321,10 @@
         <v>460</v>
       </c>
       <c r="H78" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="I78" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>593</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
@@ -8281,7 +8338,7 @@
         <v>358</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="R78" s="2" t="s">
         <v>29</v>
@@ -8292,27 +8349,29 @@
     </row>
     <row r="79" spans="1:19" ht="128.25">
       <c r="A79" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>596</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
+      <c r="F79" s="2" t="s">
+        <v>1307</v>
+      </c>
       <c r="G79" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H79" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="I79" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>599</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
@@ -8320,7 +8379,7 @@
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2" t="s">
@@ -8330,40 +8389,40 @@
         <v>40</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="R79" s="2" t="s">
         <v>29</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="80" spans="1:19" ht="128.25">
       <c r="A80" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>605</v>
+        <v>1308</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
@@ -8381,7 +8440,7 @@
         <v>40</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>29</v>
@@ -8392,40 +8451,40 @@
     </row>
     <row r="81" spans="1:19" ht="228">
       <c r="A81" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="C81" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="E81" s="2" t="s">
+      <c r="F81" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>255</v>
       </c>
       <c r="H81" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="I81" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="I81" s="2" t="s">
-        <v>613</v>
-      </c>
       <c r="J81" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="K81" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="K81" s="2" t="s">
+      <c r="L81" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -8433,13 +8492,13 @@
         <v>26</v>
       </c>
       <c r="P81" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="Q81" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="Q81" s="2" t="s">
+      <c r="R81" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="R81" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="S81" s="2" t="s">
         <v>188</v>
@@ -8447,31 +8506,31 @@
     </row>
     <row r="82" spans="1:19" ht="199.5">
       <c r="A82" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="C82" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="E82" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="F82" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G82" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="F82" s="2" t="s">
+      <c r="H82" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="I82" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>625</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
@@ -8479,7 +8538,7 @@
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2" t="s">
@@ -8489,49 +8548,49 @@
         <v>40</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="S82" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="313.5">
+    <row r="83" spans="1:19" ht="342">
       <c r="A83" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="H83" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="I83" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="J83" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -8539,13 +8598,13 @@
         <v>26</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="S83" s="2" t="s">
         <v>43</v>
@@ -8553,35 +8612,35 @@
     </row>
     <row r="84" spans="1:19" ht="142.5">
       <c r="A84" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2" t="s">
         <v>57</v>
       </c>
       <c r="H84" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="K84" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>531</v>
@@ -8595,46 +8654,46 @@
         <v>40</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="85" spans="1:19" ht="156.75">
       <c r="A85" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2" t="s">
         <v>57</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>531</v>
@@ -8648,46 +8707,46 @@
         <v>40</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="86" spans="1:19" ht="128.25">
       <c r="A86" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2" t="s">
         <v>57</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -8699,49 +8758,49 @@
         <v>40</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="87" spans="1:19" ht="156.75">
       <c r="A87" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="J87" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="J87" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
@@ -8752,7 +8811,7 @@
         <v>337</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="R87" s="2" t="s">
         <v>29</v>
@@ -8763,38 +8822,38 @@
     </row>
     <row r="88" spans="1:19" ht="171">
       <c r="A88" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="K88" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="H88" s="2" t="s">
+      <c r="L88" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="J88" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
@@ -8805,10 +8864,10 @@
         <v>40</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="S88" s="2" t="s">
         <v>43</v>
@@ -8816,34 +8875,34 @@
     </row>
     <row r="89" spans="1:19" ht="228">
       <c r="A89" s="2" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2" t="s">
         <v>355</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
       <c r="L89" s="2" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -8854,10 +8913,10 @@
         <v>40</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="S89" s="2" t="s">
         <v>43</v>
@@ -8865,34 +8924,34 @@
     </row>
     <row r="90" spans="1:19" ht="114">
       <c r="A90" s="2" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
       <c r="L90" s="2" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -8903,10 +8962,10 @@
         <v>40</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="S90" s="2" t="s">
         <v>43</v>
@@ -8914,38 +8973,38 @@
     </row>
     <row r="91" spans="1:19" ht="142.5">
       <c r="A91" s="2" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="K91" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="H91" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="J91" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>681</v>
-      </c>
       <c r="L91" s="2" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="M91" s="2" t="s">
         <v>60</v>
@@ -8958,10 +9017,10 @@
         <v>40</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="S91" s="2" t="s">
         <v>43</v>
@@ -8969,29 +9028,31 @@
     </row>
     <row r="92" spans="1:19" ht="142.5">
       <c r="A92" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="F92" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G92" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="H92" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="I92" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>717</v>
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
@@ -9000,7 +9061,7 @@
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
       <c r="N92" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="O92" s="2" t="s">
         <v>26</v>
@@ -9009,10 +9070,10 @@
         <v>109</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="S92" s="2" t="s">
         <v>43</v>
@@ -9020,37 +9081,35 @@
     </row>
     <row r="93" spans="1:19" ht="114">
       <c r="A93" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="F93" s="2"/>
+      <c r="G93" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="H93" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="I93" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="J93" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="F93" s="2" t="s">
+      <c r="K93" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="J93" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="K93" s="2" t="s">
-        <v>731</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -9059,13 +9118,13 @@
         <v>26</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="R93" s="2" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="S93" s="2" t="s">
         <v>43</v>
@@ -9073,40 +9132,40 @@
     </row>
     <row r="94" spans="1:19" ht="142.5">
       <c r="A94" s="2" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="G94" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>727</v>
-      </c>
       <c r="H94" s="2" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -9114,13 +9173,13 @@
         <v>26</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="R94" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="S94" s="2" t="s">
         <v>43</v>
@@ -9128,31 +9187,31 @@
     </row>
     <row r="95" spans="1:19" ht="142.5">
       <c r="A95" s="2" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>1317</v>
+        <v>1305</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>460</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
@@ -9167,13 +9226,13 @@
         <v>26</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="S95" s="2" t="s">
         <v>188</v>
@@ -9181,29 +9240,29 @@
     </row>
     <row r="96" spans="1:19" ht="142.5">
       <c r="A96" s="2" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
@@ -9216,13 +9275,13 @@
         <v>26</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="R96" s="2" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="S96" s="2" t="s">
         <v>43</v>
@@ -9230,48 +9289,48 @@
     </row>
     <row r="97" spans="1:19" ht="171">
       <c r="A97" s="2" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
       <c r="M97" s="2" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="R97" s="2" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="S97" s="2" t="s">
         <v>43</v>
@@ -9279,36 +9338,36 @@
     </row>
     <row r="98" spans="1:19" ht="142.5">
       <c r="A98" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="I98" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>776</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
       <c r="L98" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
@@ -9319,10 +9378,10 @@
         <v>337</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="R98" s="2" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="S98" s="2" t="s">
         <v>188</v>
@@ -9330,35 +9389,35 @@
     </row>
     <row r="99" spans="1:19" ht="399">
       <c r="A99" s="2" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -9370,10 +9429,10 @@
         <v>109</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="R99" s="2" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="S99" s="2" t="s">
         <v>188</v>
@@ -9381,40 +9440,40 @@
     </row>
     <row r="100" spans="1:19" ht="399">
       <c r="A100" s="2" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
@@ -9425,10 +9484,10 @@
         <v>109</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="R100" s="2" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="S100" s="2" t="s">
         <v>188</v>
@@ -9436,40 +9495,40 @@
     </row>
     <row r="101" spans="1:19" ht="342">
       <c r="A101" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="I101" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>805</v>
-      </c>
       <c r="J101" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="K101" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="K101" s="2" t="s">
+      <c r="L101" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="L101" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
@@ -9477,13 +9536,13 @@
         <v>26</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R101" s="2" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="S101" s="2" t="s">
         <v>188</v>
@@ -9491,36 +9550,36 @@
     </row>
     <row r="102" spans="1:19" ht="114">
       <c r="A102" s="2" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
       <c r="L102" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
@@ -9528,13 +9587,13 @@
         <v>26</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="R102" s="2" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="S102" s="2" t="s">
         <v>188</v>
@@ -9542,36 +9601,36 @@
     </row>
     <row r="103" spans="1:19" ht="228">
       <c r="A103" s="2" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
-        <v>665</v>
+        <v>1315</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
@@ -9582,7 +9641,7 @@
         <v>337</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="R103" s="2" t="s">
         <v>29</v>
@@ -9593,32 +9652,34 @@
     </row>
     <row r="104" spans="1:19" ht="142.5">
       <c r="A104" s="2" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
+      <c r="F104" s="2" t="s">
+        <v>1319</v>
+      </c>
       <c r="G104" s="2" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
       <c r="L104" s="2" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
@@ -9629,36 +9690,36 @@
         <v>337</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="R104" s="2" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="S104" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="105" spans="1:19" ht="114">
       <c r="A105" s="2" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2" t="s">
@@ -9674,7 +9735,7 @@
         <v>109</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="R105" s="2" t="s">
         <v>29</v>
@@ -9685,27 +9746,27 @@
     </row>
     <row r="106" spans="1:19" ht="142.5">
       <c r="A106" s="2" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="J106" s="2"/>
       <c r="K106" s="2" t="s">
@@ -9721,7 +9782,7 @@
         <v>109</v>
       </c>
       <c r="Q106" s="2" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="R106" s="2" t="s">
         <v>29</v>
@@ -9732,27 +9793,27 @@
     </row>
     <row r="107" spans="1:19" ht="142.5">
       <c r="A107" s="2" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="J107" s="2"/>
       <c r="K107" s="2" t="s">
@@ -9768,7 +9829,7 @@
         <v>109</v>
       </c>
       <c r="Q107" s="2" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="R107" s="2" t="s">
         <v>29</v>
@@ -9779,27 +9840,27 @@
     </row>
     <row r="108" spans="1:19" ht="171">
       <c r="A108" s="2" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="J108" s="2"/>
       <c r="K108" s="2" t="s">
@@ -9815,7 +9876,7 @@
         <v>109</v>
       </c>
       <c r="Q108" s="2" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="R108" s="2" t="s">
         <v>29</v>
@@ -9826,27 +9887,27 @@
     </row>
     <row r="109" spans="1:19" ht="142.5">
       <c r="A109" s="2" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="J109" s="2"/>
       <c r="K109" s="2" t="s">
@@ -9862,7 +9923,7 @@
         <v>109</v>
       </c>
       <c r="Q109" s="2" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="R109" s="2" t="s">
         <v>29</v>
@@ -9873,27 +9934,27 @@
     </row>
     <row r="110" spans="1:19" ht="142.5">
       <c r="A110" s="2" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="J110" s="2"/>
       <c r="K110" s="2" t="s">
@@ -9909,7 +9970,7 @@
         <v>109</v>
       </c>
       <c r="Q110" s="2" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="R110" s="2" t="s">
         <v>29</v>
@@ -9920,27 +9981,27 @@
     </row>
     <row r="111" spans="1:19" ht="142.5">
       <c r="A111" s="2" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="J111" s="2"/>
       <c r="K111" s="2" t="s">
@@ -9956,7 +10017,7 @@
         <v>109</v>
       </c>
       <c r="Q111" s="2" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="R111" s="2" t="s">
         <v>29</v>
@@ -9967,27 +10028,27 @@
     </row>
     <row r="112" spans="1:19" ht="171">
       <c r="A112" s="2" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="J112" s="2"/>
       <c r="K112" s="2" t="s">
@@ -9996,7 +10057,7 @@
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
       <c r="N112" s="2" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="O112" s="2" t="s">
         <v>26</v>
@@ -10005,7 +10066,7 @@
         <v>109</v>
       </c>
       <c r="Q112" s="2" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="R112" s="2" t="s">
         <v>29</v>
@@ -10016,16 +10077,16 @@
     </row>
     <row r="113" spans="1:19" ht="99.75">
       <c r="A113" s="2" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
@@ -10033,10 +10094,10 @@
         <v>83</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="J113" s="2"/>
       <c r="K113" s="2" t="s">
@@ -10045,16 +10106,16 @@
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="Q113" s="2" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="R113" s="2" t="s">
         <v>29</v>
@@ -10065,16 +10126,16 @@
     </row>
     <row r="114" spans="1:19" ht="114">
       <c r="A114" s="2" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
@@ -10082,10 +10143,10 @@
         <v>83</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="J114" s="2"/>
       <c r="K114" s="2" t="s">
@@ -10094,7 +10155,7 @@
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
       <c r="N114" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O114" s="2" t="s">
         <v>26</v>
@@ -10103,7 +10164,7 @@
         <v>337</v>
       </c>
       <c r="Q114" s="2" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="R114" s="2" t="s">
         <v>29</v>
@@ -10114,16 +10175,16 @@
     </row>
     <row r="115" spans="1:19" ht="99.75">
       <c r="A115" s="2" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
@@ -10131,10 +10192,10 @@
         <v>36</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="J115" s="2"/>
       <c r="K115" s="2" t="s">
@@ -10143,7 +10204,7 @@
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O115" s="2" t="s">
         <v>26</v>
@@ -10152,7 +10213,7 @@
         <v>40</v>
       </c>
       <c r="Q115" s="2" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="R115" s="2" t="s">
         <v>29</v>
@@ -10163,16 +10224,16 @@
     </row>
     <row r="116" spans="1:19" ht="99.75">
       <c r="A116" s="2" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
@@ -10180,10 +10241,10 @@
         <v>369</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2" t="s">
@@ -10192,7 +10253,7 @@
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
       <c r="N116" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O116" s="2" t="s">
         <v>26</v>
@@ -10201,7 +10262,7 @@
         <v>40</v>
       </c>
       <c r="Q116" s="2" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="R116" s="2" t="s">
         <v>29</v>
@@ -10212,16 +10273,16 @@
     </row>
     <row r="117" spans="1:19" ht="99.75">
       <c r="A117" s="2" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
@@ -10232,7 +10293,7 @@
         <v>183</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="J117" s="2"/>
       <c r="K117" s="2" t="s">
@@ -10241,16 +10302,16 @@
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
       <c r="N117" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="P117" s="2" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="Q117" s="2" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="R117" s="2" t="s">
         <v>29</v>
@@ -10261,16 +10322,16 @@
     </row>
     <row r="118" spans="1:19" ht="99.75">
       <c r="A118" s="2" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
@@ -10278,10 +10339,10 @@
         <v>380</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2" t="s">
@@ -10290,7 +10351,7 @@
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O118" s="2" t="s">
         <v>325</v>
@@ -10299,7 +10360,7 @@
         <v>40</v>
       </c>
       <c r="Q118" s="2" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="R118" s="2" t="s">
         <v>29</v>
@@ -10310,16 +10371,16 @@
     </row>
     <row r="119" spans="1:19" ht="99.75">
       <c r="A119" s="2" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
@@ -10327,10 +10388,10 @@
         <v>83</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="J119" s="2"/>
       <c r="K119" s="2" t="s">
@@ -10339,16 +10400,16 @@
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
       <c r="N119" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="P119" s="2" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="Q119" s="2" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="R119" s="2" t="s">
         <v>29</v>
@@ -10359,27 +10420,27 @@
     </row>
     <row r="120" spans="1:19" ht="114">
       <c r="A120" s="2" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="J120" s="2"/>
       <c r="K120" s="2" t="s">
@@ -10388,7 +10449,7 @@
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
       <c r="N120" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O120" s="2" t="s">
         <v>325</v>
@@ -10397,7 +10458,7 @@
         <v>40</v>
       </c>
       <c r="Q120" s="2" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="R120" s="2" t="s">
         <v>29</v>
@@ -10408,16 +10469,16 @@
     </row>
     <row r="121" spans="1:19" ht="114">
       <c r="A121" s="2" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
@@ -10425,10 +10486,10 @@
         <v>299</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="J121" s="2"/>
       <c r="K121" s="2" t="s">
@@ -10437,16 +10498,16 @@
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
       <c r="N121" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O121" s="2" t="s">
         <v>325</v>
       </c>
       <c r="P121" s="2" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="Q121" s="2" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="R121" s="2" t="s">
         <v>29</v>
@@ -10457,27 +10518,27 @@
     </row>
     <row r="122" spans="1:19" ht="142.5">
       <c r="A122" s="2" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="J122" s="2"/>
       <c r="K122" s="2" t="s">
@@ -10486,7 +10547,7 @@
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O122" s="2" t="s">
         <v>325</v>
@@ -10495,7 +10556,7 @@
         <v>40</v>
       </c>
       <c r="Q122" s="2" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="R122" s="2" t="s">
         <v>29</v>
@@ -10506,27 +10567,27 @@
     </row>
     <row r="123" spans="1:19" ht="142.5">
       <c r="A123" s="2" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="J123" s="2"/>
       <c r="K123" s="2" t="s">
@@ -10535,7 +10596,7 @@
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
       <c r="N123" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O123" s="2" t="s">
         <v>26</v>
@@ -10544,38 +10605,38 @@
         <v>109</v>
       </c>
       <c r="Q123" s="2" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="R123" s="2" t="s">
         <v>29</v>
       </c>
       <c r="S123" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="124" spans="1:19" ht="142.5">
       <c r="A124" s="2" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="J124" s="2"/>
       <c r="K124" s="2" t="s">
@@ -10584,16 +10645,16 @@
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
       <c r="N124" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="P124" s="2" t="s">
         <v>109</v>
       </c>
       <c r="Q124" s="2" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="R124" s="2" t="s">
         <v>29</v>
@@ -10604,16 +10665,16 @@
     </row>
     <row r="125" spans="1:19" ht="114">
       <c r="A125" s="2" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
@@ -10621,10 +10682,10 @@
         <v>306</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="J125" s="2"/>
       <c r="K125" s="2" t="s">
@@ -10633,16 +10694,16 @@
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
       <c r="N125" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="O125" s="2" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="P125" s="2" t="s">
         <v>109</v>
       </c>
       <c r="Q125" s="2" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="R125" s="2" t="s">
         <v>29</v>
@@ -10653,32 +10714,32 @@
     </row>
     <row r="126" spans="1:19" ht="142.5">
       <c r="A126" s="2" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
       <c r="N126" s="2" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="O126" s="2" t="s">
         <v>26</v>
@@ -10687,7 +10748,7 @@
         <v>109</v>
       </c>
       <c r="Q126" s="2" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="R126" s="2" t="s">
         <v>29</v>
@@ -10698,30 +10759,32 @@
     </row>
     <row r="127" spans="1:19" ht="114">
       <c r="A127" s="2" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
-      <c r="F127" s="2"/>
+      <c r="F127" s="2" t="s">
+        <v>1320</v>
+      </c>
       <c r="G127" s="2" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
       <c r="L127" s="2" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
@@ -10732,7 +10795,7 @@
         <v>358</v>
       </c>
       <c r="Q127" s="2" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="R127" s="2" t="s">
         <v>29</v>
@@ -10743,27 +10806,29 @@
     </row>
     <row r="128" spans="1:19" ht="199.5">
       <c r="A128" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="I128" s="2" t="s">
         <v>977</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>979</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" s="2"/>
-      <c r="G128" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>983</v>
       </c>
       <c r="J128" s="2"/>
       <c r="K128" s="2" t="s">
@@ -10771,17 +10836,17 @@
       </c>
       <c r="L128" s="2"/>
       <c r="M128" s="2" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="P128" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Q128" s="2" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="R128" s="2" t="s">
         <v>29</v>
@@ -10792,10 +10857,10 @@
     </row>
     <row r="129" spans="1:19" ht="99.75">
       <c r="A129" s="2" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>33</v>
@@ -10804,18 +10869,22 @@
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>990</v>
-      </c>
-      <c r="J129" s="2"/>
-      <c r="K129" s="2"/>
+        <v>984</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>1316</v>
+      </c>
       <c r="L129" s="2" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
@@ -10826,21 +10895,21 @@
         <v>358</v>
       </c>
       <c r="Q129" s="2" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="R129" s="2" t="s">
         <v>29</v>
       </c>
       <c r="S129" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="130" spans="1:19" ht="99.75">
       <c r="A130" s="2" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>33</v>
@@ -10852,15 +10921,15 @@
         <v>36</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="J130" s="2"/>
       <c r="K130" s="2"/>
       <c r="L130" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
@@ -10871,7 +10940,7 @@
         <v>40</v>
       </c>
       <c r="Q130" s="2" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="R130" s="2" t="s">
         <v>29</v>
@@ -10882,10 +10951,10 @@
     </row>
     <row r="131" spans="1:19" ht="99.75">
       <c r="A131" s="2" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>33</v>
@@ -10897,15 +10966,15 @@
         <v>36</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
       <c r="L131" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
@@ -10916,7 +10985,7 @@
         <v>40</v>
       </c>
       <c r="Q131" s="2" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="R131" s="2" t="s">
         <v>29</v>
@@ -10925,34 +10994,36 @@
         <v>43</v>
       </c>
     </row>
-    <row r="132" spans="1:19" ht="156.75">
+    <row r="132" spans="1:19" ht="142.5">
       <c r="A132" s="2" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
+      <c r="F132" s="2" t="s">
+        <v>1326</v>
+      </c>
       <c r="G132" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="J132" s="2"/>
       <c r="K132" s="2"/>
       <c r="L132" s="2" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
@@ -10963,44 +11034,40 @@
         <v>337</v>
       </c>
       <c r="Q132" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="R132" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="S132" s="2" t="s">
-        <v>652</v>
-      </c>
+        <v>1318</v>
+      </c>
+      <c r="R132" s="2"/>
+      <c r="S132" s="2"/>
     </row>
     <row r="133" spans="1:19" ht="156.75">
       <c r="A133" s="2" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="J133" s="2"/>
       <c r="K133" s="2" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -11012,7 +11079,7 @@
         <v>27</v>
       </c>
       <c r="Q133" s="2" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="R133" s="2" t="s">
         <v>29</v>
@@ -11023,33 +11090,33 @@
     </row>
     <row r="134" spans="1:19" ht="156.75">
       <c r="A134" s="2" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="J134" s="2"/>
       <c r="K134" s="2" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -11061,7 +11128,7 @@
         <v>27</v>
       </c>
       <c r="Q134" s="2" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="R134" s="2" t="s">
         <v>29</v>
@@ -11072,29 +11139,29 @@
     </row>
     <row r="135" spans="1:19" ht="171">
       <c r="A135" s="2" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="J135" s="2"/>
       <c r="K135" s="2" t="s">
@@ -11102,7 +11169,7 @@
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2" t="s">
@@ -11112,7 +11179,7 @@
         <v>27</v>
       </c>
       <c r="Q135" s="2" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="R135" s="2" t="s">
         <v>29</v>
@@ -11123,52 +11190,52 @@
     </row>
     <row r="136" spans="1:19" ht="114">
       <c r="A136" s="2" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" s="2" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>426</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P136" s="2" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="Q136" s="2" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="R136" s="2" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="S136" s="2" t="s">
         <v>43</v>
@@ -11176,38 +11243,38 @@
     </row>
     <row r="137" spans="1:19" ht="199.5">
       <c r="A137" s="2" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="J137" s="2"/>
       <c r="K137" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
@@ -11215,13 +11282,13 @@
         <v>26</v>
       </c>
       <c r="P137" s="2" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="Q137" s="2" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="R137" s="2" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="S137" s="2" t="s">
         <v>188</v>
@@ -11229,35 +11296,35 @@
     </row>
     <row r="138" spans="1:19" ht="399">
       <c r="A138" s="2" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="J138" s="2"/>
       <c r="K138" s="2" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -11269,10 +11336,10 @@
         <v>109</v>
       </c>
       <c r="Q138" s="2" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="R138" s="2" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="S138" s="2" t="s">
         <v>188</v>
@@ -11280,38 +11347,38 @@
     </row>
     <row r="139" spans="1:19" ht="399">
       <c r="A139" s="2" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="D139" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E139" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="E139" s="2" t="s">
-        <v>1057</v>
-      </c>
       <c r="F139" s="2" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="J139" s="2"/>
       <c r="K139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L139" s="2" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
@@ -11322,10 +11389,10 @@
         <v>109</v>
       </c>
       <c r="Q139" s="2" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="R139" s="2" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="S139" s="2" t="s">
         <v>188</v>
@@ -11333,35 +11400,35 @@
     </row>
     <row r="140" spans="1:19" ht="128.25">
       <c r="A140" s="2" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" s="2" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
       <c r="L140" s="2"/>
       <c r="M140" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2" t="s">
@@ -11371,45 +11438,45 @@
         <v>40</v>
       </c>
       <c r="Q140" s="2" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="R140" s="2" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="S140" s="2" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="141" spans="1:19" ht="156.75">
+    <row r="141" spans="1:19" ht="171">
       <c r="A141" s="2" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>1073</v>
+        <v>1322</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>1074</v>
+        <v>1066</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>1075</v>
+        <v>1067</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>1076</v>
+        <v>1068</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>1077</v>
+        <v>1069</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>25</v>
@@ -11423,13 +11490,13 @@
         <v>26</v>
       </c>
       <c r="P141" s="2" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="Q141" s="2" t="s">
-        <v>1079</v>
+        <v>1071</v>
       </c>
       <c r="R141" s="2" t="s">
-        <v>1080</v>
+        <v>1072</v>
       </c>
       <c r="S141" s="2" t="s">
         <v>188</v>
@@ -11437,52 +11504,52 @@
     </row>
     <row r="142" spans="1:19" ht="356.25">
       <c r="A142" s="2" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1082</v>
+        <v>1074</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>76</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>1084</v>
+        <v>1076</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>1085</v>
+        <v>1077</v>
       </c>
       <c r="J142" s="2"/>
       <c r="K142" s="2" t="s">
-        <v>1086</v>
+        <v>1078</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="M142" s="2" t="s">
-        <v>1088</v>
+        <v>1080</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
       <c r="P142" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Q142" s="2" t="s">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="R142" s="2" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="S142" s="2" t="s">
         <v>328</v>
@@ -11490,37 +11557,37 @@
     </row>
     <row r="143" spans="1:19" ht="199.5">
       <c r="A143" s="2" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1092</v>
+        <v>1084</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>1093</v>
+        <v>1085</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>1094</v>
+        <v>1086</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>1096</v>
+        <v>1088</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
       <c r="J143" s="2"/>
       <c r="K143" s="2" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2" t="s">
@@ -11530,10 +11597,10 @@
         <v>40</v>
       </c>
       <c r="Q143" s="2" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
       <c r="R143" s="2" t="s">
-        <v>1099</v>
+        <v>1091</v>
       </c>
       <c r="S143" s="2" t="s">
         <v>30</v>
@@ -11541,31 +11608,31 @@
     </row>
     <row r="144" spans="1:19" ht="285">
       <c r="A144" s="2" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1101</v>
+        <v>1093</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>1102</v>
+        <v>1094</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1103</v>
+        <v>1095</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>1104</v>
+        <v>1096</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>1105</v>
+        <v>1321</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>460</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>1106</v>
+        <v>1097</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>1107</v>
+        <v>1098</v>
       </c>
       <c r="J144" s="2"/>
       <c r="K144" s="2" t="s">
@@ -11573,7 +11640,7 @@
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2" t="s">
-        <v>1108</v>
+        <v>1099</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2" t="s">
@@ -11583,10 +11650,10 @@
         <v>40</v>
       </c>
       <c r="Q144" s="2" t="s">
-        <v>1109</v>
+        <v>1100</v>
       </c>
       <c r="R144" s="2" t="s">
-        <v>1110</v>
+        <v>1101</v>
       </c>
       <c r="S144" s="2" t="s">
         <v>43</v>
@@ -11594,38 +11661,38 @@
     </row>
     <row r="145" spans="1:19" ht="114">
       <c r="A145" s="2" t="s">
-        <v>1111</v>
+        <v>1102</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1112</v>
+        <v>1103</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>167</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>1112</v>
+        <v>1103</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>1113</v>
+        <v>1104</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>1114</v>
+        <v>1328</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>1115</v>
+        <v>1105</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>1116</v>
+        <v>1106</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>1117</v>
+        <v>1107</v>
       </c>
       <c r="J145" s="2"/>
       <c r="K145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L145" s="2" t="s">
-        <v>1118</v>
+        <v>1108</v>
       </c>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
@@ -11636,10 +11703,10 @@
         <v>40</v>
       </c>
       <c r="Q145" s="2" t="s">
-        <v>1119</v>
+        <v>1109</v>
       </c>
       <c r="R145" s="2" t="s">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="S145" s="2" t="s">
         <v>43</v>
@@ -11647,29 +11714,29 @@
     </row>
     <row r="146" spans="1:19" ht="114">
       <c r="A146" s="2" t="s">
-        <v>1121</v>
+        <v>1111</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1122</v>
+        <v>1112</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>1123</v>
+        <v>1113</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" s="2" t="s">
-        <v>1124</v>
+        <v>1114</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>1125</v>
+        <v>1327</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>1126</v>
+        <v>1115</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>1127</v>
+        <v>1116</v>
       </c>
       <c r="J146" s="2"/>
       <c r="K146" s="2" t="s">
@@ -11677,7 +11744,7 @@
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2" t="s">
-        <v>1128</v>
+        <v>1117</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2" t="s">
@@ -11687,10 +11754,10 @@
         <v>40</v>
       </c>
       <c r="Q146" s="2" t="s">
-        <v>1129</v>
+        <v>1118</v>
       </c>
       <c r="R146" s="2" t="s">
-        <v>1130</v>
+        <v>1119</v>
       </c>
       <c r="S146" s="2" t="s">
         <v>43</v>
@@ -11698,16 +11765,16 @@
     </row>
     <row r="147" spans="1:19" ht="114">
       <c r="A147" s="2" t="s">
-        <v>1131</v>
+        <v>1120</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1132</v>
+        <v>1121</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>1133</v>
+        <v>1122</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
@@ -11715,10 +11782,10 @@
         <v>36</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>1134</v>
+        <v>1123</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>1135</v>
+        <v>1124</v>
       </c>
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
@@ -11734,7 +11801,7 @@
         <v>40</v>
       </c>
       <c r="Q147" s="2" t="s">
-        <v>1136</v>
+        <v>1125</v>
       </c>
       <c r="R147" s="2" t="s">
         <v>29</v>
@@ -11745,34 +11812,36 @@
     </row>
     <row r="148" spans="1:19" ht="114">
       <c r="A148" s="2" t="s">
-        <v>1137</v>
+        <v>1126</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1138</v>
+        <v>1127</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>1139</v>
+        <v>1128</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>1140</v>
+        <v>1129</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F148" s="2"/>
+        <v>1130</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>1325</v>
+      </c>
       <c r="G148" s="2" t="s">
-        <v>1142</v>
+        <v>1131</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>1143</v>
+        <v>1132</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>1144</v>
+        <v>1133</v>
       </c>
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
       <c r="L148" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
@@ -11780,13 +11849,13 @@
         <v>26</v>
       </c>
       <c r="P148" s="2" t="s">
-        <v>1145</v>
+        <v>1134</v>
       </c>
       <c r="Q148" s="2" t="s">
-        <v>1146</v>
+        <v>1135</v>
       </c>
       <c r="R148" s="2" t="s">
-        <v>1147</v>
+        <v>1136</v>
       </c>
       <c r="S148" s="2" t="s">
         <v>188</v>
@@ -11794,34 +11863,36 @@
     </row>
     <row r="149" spans="1:19" ht="114">
       <c r="A149" s="2" t="s">
-        <v>1148</v>
+        <v>1137</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1149</v>
+        <v>1138</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>1150</v>
+        <v>1139</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>1149</v>
+        <v>1138</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F149" s="2"/>
+        <v>1140</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>1324</v>
+      </c>
       <c r="G149" s="2" t="s">
-        <v>1142</v>
+        <v>1131</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>1143</v>
+        <v>1132</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>1152</v>
+        <v>1141</v>
       </c>
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
       <c r="L149" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
@@ -11832,10 +11903,10 @@
         <v>258</v>
       </c>
       <c r="Q149" s="2" t="s">
-        <v>1153</v>
+        <v>1142</v>
       </c>
       <c r="R149" s="2" t="s">
-        <v>1154</v>
+        <v>1143</v>
       </c>
       <c r="S149" s="2" t="s">
         <v>188</v>
@@ -11843,13 +11914,13 @@
     </row>
     <row r="150" spans="1:19" ht="99.75">
       <c r="A150" s="2" t="s">
-        <v>1155</v>
+        <v>1144</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1155</v>
+        <v>1144</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>1156</v>
+        <v>1145</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
@@ -11858,15 +11929,15 @@
         <v>380</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>1157</v>
+        <v>1146</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>1158</v>
+        <v>1147</v>
       </c>
       <c r="J150" s="2"/>
       <c r="K150" s="2"/>
       <c r="L150" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
@@ -11877,7 +11948,7 @@
         <v>40</v>
       </c>
       <c r="Q150" s="2" t="s">
-        <v>1159</v>
+        <v>1148</v>
       </c>
       <c r="R150" s="2" t="s">
         <v>29</v>
@@ -11888,10 +11959,10 @@
     </row>
     <row r="151" spans="1:19" ht="99.75">
       <c r="A151" s="2" t="s">
-        <v>1160</v>
+        <v>1149</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1160</v>
+        <v>1149</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>33</v>
@@ -11903,15 +11974,15 @@
         <v>76</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>1161</v>
+        <v>1150</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>1162</v>
+        <v>1151</v>
       </c>
       <c r="J151" s="2"/>
       <c r="K151" s="2"/>
       <c r="L151" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
@@ -11922,7 +11993,7 @@
         <v>40</v>
       </c>
       <c r="Q151" s="2" t="s">
-        <v>1163</v>
+        <v>1152</v>
       </c>
       <c r="R151" s="2" t="s">
         <v>29</v>
@@ -11933,10 +12004,10 @@
     </row>
     <row r="152" spans="1:19" ht="99.75">
       <c r="A152" s="2" t="s">
-        <v>1164</v>
+        <v>1153</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1165</v>
+        <v>1154</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>33</v>
@@ -11948,15 +12019,15 @@
         <v>148</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>1166</v>
+        <v>1155</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>1167</v>
+        <v>1156</v>
       </c>
       <c r="J152" s="2"/>
       <c r="K152" s="2"/>
       <c r="L152" s="2" t="s">
-        <v>1168</v>
+        <v>1157</v>
       </c>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
@@ -11967,7 +12038,7 @@
         <v>40</v>
       </c>
       <c r="Q152" s="2" t="s">
-        <v>1169</v>
+        <v>1158</v>
       </c>
       <c r="R152" s="2" t="s">
         <v>29</v>
@@ -11978,31 +12049,31 @@
     </row>
     <row r="153" spans="1:19" ht="114">
       <c r="A153" s="2" t="s">
-        <v>1170</v>
+        <v>1159</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1171</v>
+        <v>1160</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>1172</v>
+        <v>1161</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1173</v>
+        <v>1162</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>1174</v>
+        <v>1163</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>363</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>1175</v>
+        <v>1164</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>1176</v>
+        <v>1165</v>
       </c>
       <c r="J153" s="2"/>
       <c r="K153" s="2" t="s">
@@ -12014,16 +12085,16 @@
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
       <c r="O153" s="2" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="P153" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Q153" s="2" t="s">
-        <v>1177</v>
+        <v>1166</v>
       </c>
       <c r="R153" s="2" t="s">
-        <v>1178</v>
+        <v>1167</v>
       </c>
       <c r="S153" s="2" t="s">
         <v>328</v>
@@ -12031,34 +12102,34 @@
     </row>
     <row r="154" spans="1:19" ht="228">
       <c r="A154" s="2" t="s">
-        <v>1179</v>
+        <v>1168</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>1180</v>
+        <v>1169</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>1181</v>
+        <v>1170</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>1182</v>
+        <v>1171</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>1183</v>
+        <v>1172</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>1184</v>
+        <v>1173</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>1185</v>
+        <v>1174</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>1186</v>
+        <v>1175</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>1187</v>
+        <v>1176</v>
       </c>
       <c r="K154" s="2" t="s">
         <v>25</v>
@@ -12075,10 +12146,10 @@
         <v>61</v>
       </c>
       <c r="Q154" s="2" t="s">
-        <v>1188</v>
+        <v>1177</v>
       </c>
       <c r="R154" s="2" t="s">
-        <v>1189</v>
+        <v>1178</v>
       </c>
       <c r="S154" s="2" t="s">
         <v>188</v>
@@ -12086,35 +12157,35 @@
     </row>
     <row r="155" spans="1:19" ht="199.5">
       <c r="A155" s="2" t="s">
-        <v>1190</v>
+        <v>1179</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>1181</v>
+        <v>1170</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D155" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F155" s="2" t="s">
         <v>1181</v>
       </c>
-      <c r="E155" s="2" t="s">
-        <v>1191</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>1192</v>
-      </c>
       <c r="G155" s="2" t="s">
-        <v>1193</v>
+        <v>1182</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>1194</v>
+        <v>1183</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>1195</v>
+        <v>1184</v>
       </c>
       <c r="J155" s="2"/>
       <c r="K155" s="2" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -12123,13 +12194,13 @@
         <v>26</v>
       </c>
       <c r="P155" s="2" t="s">
-        <v>1196</v>
+        <v>1185</v>
       </c>
       <c r="Q155" s="2" t="s">
-        <v>1197</v>
+        <v>1186</v>
       </c>
       <c r="R155" s="2" t="s">
-        <v>1198</v>
+        <v>1187</v>
       </c>
       <c r="S155" s="2" t="s">
         <v>188</v>
@@ -12137,34 +12208,34 @@
     </row>
     <row r="156" spans="1:19" ht="399">
       <c r="A156" s="2" t="s">
-        <v>1199</v>
+        <v>1188</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>1181</v>
+        <v>1170</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>1181</v>
+        <v>1170</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>1201</v>
+        <v>1190</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>1202</v>
+        <v>1191</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>1203</v>
+        <v>1192</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>1204</v>
+        <v>1193</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>1205</v>
+        <v>1194</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>25</v>
@@ -12183,10 +12254,10 @@
         <v>61</v>
       </c>
       <c r="Q156" s="2" t="s">
-        <v>1206</v>
+        <v>1195</v>
       </c>
       <c r="R156" s="2" t="s">
-        <v>1207</v>
+        <v>1196</v>
       </c>
       <c r="S156" s="2" t="s">
         <v>188</v>
@@ -12194,25 +12265,27 @@
     </row>
     <row r="157" spans="1:19" ht="99.75">
       <c r="A157" s="2" t="s">
-        <v>1208</v>
+        <v>1197</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>1209</v>
+        <v>1198</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
-      <c r="F157" s="2"/>
+      <c r="F157" s="2" t="s">
+        <v>1323</v>
+      </c>
       <c r="G157" s="2" t="s">
-        <v>1210</v>
+        <v>1199</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>1211</v>
+        <v>1200</v>
       </c>
       <c r="I157" s="2" t="s">
-        <v>1212</v>
+        <v>1201</v>
       </c>
       <c r="J157" s="2"/>
       <c r="K157" s="2"/>
@@ -12226,7 +12299,7 @@
         <v>358</v>
       </c>
       <c r="Q157" s="2" t="s">
-        <v>1213</v>
+        <v>1202</v>
       </c>
       <c r="R157" s="2" t="s">
         <v>29</v>
@@ -12235,41 +12308,41 @@
         <v>197</v>
       </c>
     </row>
-    <row r="158" spans="1:19" ht="142.5">
+    <row r="158" spans="1:19" ht="199.5">
       <c r="A158" s="2" t="s">
-        <v>1214</v>
+        <v>1203</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>1215</v>
+        <v>1204</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>1123</v>
+        <v>1113</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" s="2" t="s">
-        <v>1124</v>
+        <v>1114</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>1216</v>
+        <v>1329</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>1217</v>
+        <v>1205</v>
       </c>
       <c r="I158" s="2" t="s">
-        <v>1218</v>
+        <v>1206</v>
       </c>
       <c r="J158" s="2"/>
       <c r="K158" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L158" s="2" t="s">
-        <v>1219</v>
+        <v>1207</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>1128</v>
+        <v>1117</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2" t="s">
@@ -12279,16 +12352,20 @@
         <v>40</v>
       </c>
       <c r="Q158" s="2" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="R158" s="2" t="s">
-        <v>1130</v>
+        <v>1119</v>
       </c>
       <c r="S158" s="2" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F148" r:id="rId1" xr:uid="{F7419146-4E0F-4336-86A4-DFA023C36477}"/>
+    <hyperlink ref="F149" r:id="rId2" xr:uid="{3D6E06A0-3086-447A-A043-7632F77FC3BC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12306,274 +12383,274 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15">
       <c r="A1" s="1" t="s">
-        <v>1221</v>
+        <v>1209</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1222</v>
+        <v>1210</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1223</v>
+        <v>1211</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1224</v>
+        <v>1212</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1225</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.5">
       <c r="A2" s="2" t="s">
-        <v>1226</v>
+        <v>1214</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1230</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1232</v>
+        <v>1220</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1233</v>
+        <v>1221</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1234</v>
+        <v>1222</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.5">
       <c r="A4" s="2" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1237</v>
+        <v>1225</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1238</v>
+        <v>1226</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1239</v>
+        <v>1227</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.5">
       <c r="A5" s="2" t="s">
-        <v>1241</v>
+        <v>1229</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1243</v>
+        <v>1231</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1244</v>
+        <v>1232</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1245</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.5">
       <c r="A6" s="2" t="s">
-        <v>1246</v>
+        <v>1234</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1247</v>
+        <v>1235</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1248</v>
+        <v>1236</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1249</v>
+        <v>1237</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1250</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.5">
       <c r="A7" s="2" t="s">
-        <v>1251</v>
+        <v>1239</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1252</v>
+        <v>1240</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1253</v>
+        <v>1241</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1254</v>
+        <v>1242</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1255</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.5">
       <c r="A8" s="2" t="s">
-        <v>1256</v>
+        <v>1244</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1257</v>
+        <v>1245</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1259</v>
+        <v>1247</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1260</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.5">
       <c r="A9" s="2" t="s">
-        <v>1261</v>
+        <v>1249</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1262</v>
+        <v>1250</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1263</v>
+        <v>1251</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1264</v>
+        <v>1252</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1265</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.5">
       <c r="A10" s="2" t="s">
-        <v>1266</v>
+        <v>1254</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1267</v>
+        <v>1255</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1268</v>
+        <v>1256</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1269</v>
+        <v>1257</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1270</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>1271</v>
+        <v>1259</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1272</v>
+        <v>1260</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1273</v>
+        <v>1261</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1275</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>1276</v>
+        <v>1264</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1276</v>
+        <v>1264</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1279</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>1280</v>
+        <v>1268</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1281</v>
+        <v>1269</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1282</v>
+        <v>1270</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1283</v>
+        <v>1271</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1284</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.5">
       <c r="A14" s="2" t="s">
-        <v>1285</v>
+        <v>1273</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1286</v>
+        <v>1274</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1287</v>
+        <v>1275</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1288</v>
+        <v>1276</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1289</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.5">
       <c r="A15" s="2" t="s">
-        <v>1290</v>
+        <v>1278</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1291</v>
+        <v>1279</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1292</v>
+        <v>1280</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1293</v>
+        <v>1281</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1294</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>1295</v>
+        <v>1283</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1296</v>
+        <v>1284</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1297</v>
+        <v>1285</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1298</v>
+        <v>1286</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1299</v>
+        <v>1287</v>
       </c>
     </row>
   </sheetData>
@@ -12601,13 +12678,13 @@
         <v>9</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1315</v>
+        <v>1303</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1314</v>
+        <v>1302</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1313</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -12616,10 +12693,10 @@
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -12629,10 +12706,10 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -12642,10 +12719,10 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -12655,10 +12732,10 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E5" s="3"/>
     </row>
@@ -12668,10 +12745,10 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -12681,10 +12758,10 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -12694,10 +12771,10 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -12707,10 +12784,10 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -12720,10 +12797,10 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E10" s="3"/>
     </row>
@@ -12733,10 +12810,10 @@
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E11" s="3"/>
     </row>
@@ -12746,10 +12823,10 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E12" s="3"/>
     </row>
@@ -12759,10 +12836,10 @@
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E13" s="3"/>
     </row>
@@ -12772,10 +12849,10 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E14" s="3"/>
     </row>
@@ -12785,10 +12862,10 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E15" s="3"/>
     </row>
@@ -12798,10 +12875,10 @@
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E16" s="3"/>
     </row>
@@ -12811,10 +12888,10 @@
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E17" s="3"/>
     </row>
@@ -12824,10 +12901,10 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E18" s="3"/>
     </row>
@@ -12837,10 +12914,10 @@
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E19" s="3"/>
     </row>
@@ -12850,10 +12927,10 @@
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E20" s="3"/>
     </row>
@@ -12863,10 +12940,10 @@
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E21" s="3"/>
     </row>
@@ -12876,10 +12953,10 @@
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E22" s="3"/>
     </row>
@@ -12889,10 +12966,10 @@
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E23" s="3"/>
     </row>
@@ -12902,10 +12979,10 @@
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E24" s="3"/>
     </row>
@@ -12915,10 +12992,10 @@
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3" t="s">
-        <v>1307</v>
+        <v>1295</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E25" s="3"/>
     </row>
@@ -12928,10 +13005,10 @@
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3" t="s">
-        <v>1310</v>
+        <v>1298</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E26" s="3"/>
     </row>
@@ -12941,10 +13018,10 @@
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E27" s="3"/>
     </row>
@@ -12954,10 +13031,10 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E28" s="3"/>
     </row>
@@ -12967,10 +13044,10 @@
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E29" s="3"/>
     </row>
@@ -12980,10 +13057,10 @@
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E30" s="3"/>
     </row>
@@ -12993,10 +13070,10 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E31" s="3"/>
     </row>
@@ -13006,10 +13083,10 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E32" s="3"/>
     </row>
@@ -13019,10 +13096,10 @@
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E33" s="3"/>
     </row>
@@ -13032,10 +13109,10 @@
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E34" s="3"/>
     </row>
@@ -13045,10 +13122,10 @@
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E35" s="3"/>
     </row>
@@ -13058,10 +13135,10 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E36" s="3"/>
     </row>
@@ -13071,10 +13148,10 @@
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E37" s="3"/>
     </row>
@@ -13084,10 +13161,10 @@
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E38" s="3"/>
     </row>
@@ -13097,10 +13174,10 @@
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E39" s="3"/>
     </row>
@@ -13110,10 +13187,10 @@
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E40" s="3"/>
     </row>
@@ -13123,10 +13200,10 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E41" s="3"/>
     </row>
@@ -13136,10 +13213,10 @@
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E42" s="3"/>
     </row>
@@ -13149,10 +13226,10 @@
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E43" s="3"/>
     </row>
@@ -13162,10 +13239,10 @@
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E44" s="3"/>
     </row>
@@ -13177,10 +13254,10 @@
         <v>323</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E45" s="3"/>
     </row>
@@ -13192,10 +13269,10 @@
         <v>336</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E46" s="3"/>
     </row>
@@ -13205,10 +13282,10 @@
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E47" s="3"/>
     </row>
@@ -13218,10 +13295,10 @@
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E48" s="3"/>
     </row>
@@ -13231,10 +13308,10 @@
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E49" s="3"/>
     </row>
@@ -13244,10 +13321,10 @@
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E50" s="3"/>
     </row>
@@ -13257,10 +13334,10 @@
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E51" s="3"/>
     </row>
@@ -13270,10 +13347,10 @@
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E52" s="3"/>
     </row>
@@ -13283,10 +13360,10 @@
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E53" s="3"/>
     </row>
@@ -13296,10 +13373,10 @@
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E54" s="3"/>
     </row>
@@ -13309,10 +13386,10 @@
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E55" s="3"/>
     </row>
@@ -13322,10 +13399,10 @@
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E56" s="3"/>
     </row>
@@ -13335,10 +13412,10 @@
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E57" s="3"/>
     </row>
@@ -13348,10 +13425,10 @@
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E58" s="3"/>
     </row>
@@ -13361,10 +13438,10 @@
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E59" s="3"/>
     </row>
@@ -13374,10 +13451,10 @@
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E60" s="3"/>
     </row>
@@ -13387,10 +13464,10 @@
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E61" s="3"/>
     </row>
@@ -13402,10 +13479,10 @@
         <v>453</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E62" s="3"/>
     </row>
@@ -13415,10 +13492,10 @@
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E63" s="3"/>
     </row>
@@ -13428,10 +13505,10 @@
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E64" s="3"/>
     </row>
@@ -13441,10 +13518,10 @@
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E65" s="3"/>
     </row>
@@ -13454,10 +13531,10 @@
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E66" s="3"/>
     </row>
@@ -13467,10 +13544,10 @@
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E67" s="3"/>
     </row>
@@ -13480,10 +13557,10 @@
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E68" s="3"/>
     </row>
@@ -13493,10 +13570,10 @@
       </c>
       <c r="B69" s="3"/>
       <c r="C69" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E69" s="3"/>
     </row>
@@ -13506,10 +13583,10 @@
       </c>
       <c r="B70" s="3"/>
       <c r="C70" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E70" s="3"/>
     </row>
@@ -13519,10 +13596,10 @@
       </c>
       <c r="B71" s="3"/>
       <c r="C71" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E71" s="3"/>
     </row>
@@ -13532,10 +13609,10 @@
       </c>
       <c r="B72" s="3"/>
       <c r="C72" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E72" s="3"/>
     </row>
@@ -13545,10 +13622,10 @@
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E73" s="3"/>
     </row>
@@ -13558,10 +13635,10 @@
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E74" s="3"/>
     </row>
@@ -13571,10 +13648,10 @@
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E75" s="3"/>
     </row>
@@ -13584,1112 +13661,1112 @@
       </c>
       <c r="B76" s="3"/>
       <c r="C76" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E76" s="3"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1308</v>
+        <v>1296</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E77" s="3"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E78" s="3"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B79" s="3"/>
       <c r="C79" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E79" s="3"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E80" s="3"/>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1308</v>
+        <v>1296</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E81" s="3"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E82" s="3"/>
     </row>
     <row r="83" spans="1:5" ht="185.25">
       <c r="A83" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E83" s="3"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="3" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
       <c r="E84" s="3"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="3" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
       <c r="E85" s="3"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1312</v>
+        <v>1300</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
       <c r="E86" s="3"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E87" s="3"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="3" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
       <c r="E88" s="3"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="3" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E89" s="3"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="3" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E90" s="3"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="3" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
       <c r="E91" s="3"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="3" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E92" s="3"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="3" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1311</v>
+        <v>1299</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
       <c r="E93" s="3"/>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="3" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>1308</v>
+        <v>1296</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
       <c r="E94" s="3"/>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="3" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E95" s="3"/>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="3" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="3" t="s">
-        <v>1310</v>
+        <v>1298</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E96" s="3"/>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="3" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E97" s="3"/>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="3" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E98" s="3"/>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="3" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1304</v>
+        <v>1292</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
       <c r="E99" s="3"/>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="3" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E100" s="3"/>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="3" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1308</v>
+        <v>1296</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E101" s="3"/>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="3" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E102" s="3"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="3" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E103" s="3"/>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="3" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="B104" s="3"/>
       <c r="C104" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E104" s="3"/>
     </row>
     <row r="105" spans="1:5" ht="28.5">
       <c r="A105" s="3" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="3" t="s">
-        <v>1307</v>
+        <v>1295</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E105" s="3"/>
     </row>
     <row r="106" spans="1:5" ht="28.5">
       <c r="A106" s="3" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3" t="s">
-        <v>1307</v>
+        <v>1295</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E106" s="3"/>
     </row>
     <row r="107" spans="1:5" ht="28.5">
       <c r="A107" s="3" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="B107" s="3"/>
       <c r="C107" s="3" t="s">
-        <v>1307</v>
+        <v>1295</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E107" s="3"/>
     </row>
     <row r="108" spans="1:5" ht="28.5">
       <c r="A108" s="3" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="B108" s="3"/>
       <c r="C108" s="3" t="s">
-        <v>1307</v>
+        <v>1295</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E108" s="3"/>
     </row>
     <row r="109" spans="1:5" ht="28.5">
       <c r="A109" s="3" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="B109" s="3"/>
       <c r="C109" s="3" t="s">
-        <v>1307</v>
+        <v>1295</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E109" s="3"/>
     </row>
     <row r="110" spans="1:5" ht="28.5">
       <c r="A110" s="3" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3" t="s">
-        <v>1307</v>
+        <v>1295</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E110" s="3"/>
     </row>
     <row r="111" spans="1:5" ht="28.5">
       <c r="A111" s="3" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="B111" s="3"/>
       <c r="C111" s="3" t="s">
-        <v>1307</v>
+        <v>1295</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E111" s="3"/>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="3" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E112" s="3"/>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="3" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E113" s="3"/>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="3" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E114" s="3"/>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="3" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="B115" s="3"/>
       <c r="C115" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E115" s="3"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="3" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E116" s="3"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="3" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="B117" s="3"/>
       <c r="C117" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E117" s="3"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="3" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E118" s="3"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="3" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E119" s="3"/>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="3" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E120" s="3"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="3" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E121" s="3"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="3" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E122" s="3"/>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="3" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E123" s="3"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="3" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="B124" s="3"/>
       <c r="C124" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E124" s="3"/>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="3" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E125" s="3"/>
     </row>
     <row r="126" spans="1:5" ht="28.5">
       <c r="A126" s="3" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="B126" s="3"/>
       <c r="C126" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E126" s="3"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="3" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="B127" s="3"/>
       <c r="C127" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E127" s="3"/>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="3" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E128" s="3"/>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="3" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="B129" s="3"/>
       <c r="C129" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E129" s="3"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="3" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="B130" s="3"/>
       <c r="C130" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E130" s="3"/>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="3" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="B131" s="3"/>
       <c r="C131" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E131" s="3"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="3" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="B132" s="3"/>
       <c r="C132" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E132" s="3"/>
     </row>
     <row r="133" spans="1:5" ht="28.5">
       <c r="A133" s="3" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3" t="s">
-        <v>1304</v>
+        <v>1292</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E133" s="3"/>
     </row>
     <row r="134" spans="1:5" ht="28.5">
       <c r="A134" s="3" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="B134" s="3"/>
       <c r="C134" s="3" t="s">
-        <v>1304</v>
+        <v>1292</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E134" s="3"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="3" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="B135" s="3"/>
       <c r="C135" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E135" s="3"/>
     </row>
     <row r="136" spans="1:5" ht="57">
       <c r="A136" s="3" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E136" s="3"/>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="3" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="B137" s="3"/>
       <c r="C137" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E137" s="3"/>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="3" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="B138" s="3"/>
       <c r="C138" s="3" t="s">
-        <v>1304</v>
+        <v>1292</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E138" s="3"/>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="3" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E139" s="3"/>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="3" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="B140" s="3"/>
       <c r="C140" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E140" s="3"/>
     </row>
     <row r="141" spans="1:5" ht="28.5">
       <c r="A141" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B141" s="3" t="s">
         <v>1069</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>1077</v>
-      </c>
       <c r="C141" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E141" s="3"/>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="3" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
       <c r="B142" s="3"/>
       <c r="C142" s="3" t="s">
-        <v>1305</v>
+        <v>1293</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E142" s="3"/>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B143" s="3"/>
       <c r="C143" s="3" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E143" s="3"/>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="3" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="B144" s="3"/>
       <c r="C144" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E144" s="3"/>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="3" t="s">
-        <v>1111</v>
+        <v>1102</v>
       </c>
       <c r="B145" s="3"/>
       <c r="C145" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E145" s="3"/>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="3" t="s">
-        <v>1121</v>
+        <v>1111</v>
       </c>
       <c r="B146" s="3"/>
       <c r="C146" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E146" s="3"/>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="3" t="s">
-        <v>1131</v>
+        <v>1120</v>
       </c>
       <c r="B147" s="3"/>
       <c r="C147" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E147" s="3"/>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="3" t="s">
-        <v>1137</v>
+        <v>1126</v>
       </c>
       <c r="B148" s="3"/>
       <c r="C148" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E148" s="3"/>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="3" t="s">
-        <v>1148</v>
+        <v>1137</v>
       </c>
       <c r="B149" s="3"/>
       <c r="C149" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E149" s="3"/>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="3" t="s">
-        <v>1155</v>
+        <v>1144</v>
       </c>
       <c r="B150" s="3"/>
       <c r="C150" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E150" s="3"/>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="3" t="s">
-        <v>1160</v>
+        <v>1149</v>
       </c>
       <c r="B151" s="3"/>
       <c r="C151" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E151" s="3"/>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="3" t="s">
-        <v>1164</v>
+        <v>1153</v>
       </c>
       <c r="B152" s="3"/>
       <c r="C152" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E152" s="3"/>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="3" t="s">
-        <v>1170</v>
+        <v>1159</v>
       </c>
       <c r="B153" s="3"/>
       <c r="C153" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E153" s="3"/>
     </row>
     <row r="154" spans="1:5" ht="85.5">
       <c r="A154" s="3" t="s">
-        <v>1179</v>
+        <v>1168</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>1187</v>
+        <v>1176</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E154" s="3"/>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="3" t="s">
-        <v>1190</v>
+        <v>1179</v>
       </c>
       <c r="B155" s="3"/>
       <c r="C155" s="3" t="s">
-        <v>1304</v>
+        <v>1292</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E155" s="3"/>
     </row>
     <row r="156" spans="1:5" ht="28.5">
       <c r="A156" s="3" t="s">
-        <v>1199</v>
+        <v>1188</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>1205</v>
+        <v>1194</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="E156" s="3"/>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="3" t="s">
-        <v>1208</v>
+        <v>1197</v>
       </c>
       <c r="B157" s="3"/>
       <c r="C157" s="3" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E157" s="3"/>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="3" t="s">
-        <v>1214</v>
+        <v>1203</v>
       </c>
       <c r="B158" s="3"/>
       <c r="C158" s="3" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E158" s="3"/>
     </row>
@@ -14723,77 +14800,77 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="28.5">
       <c r="A8" s="3" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="28.5">
       <c r="A9" s="3" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="28.5">
       <c r="A10" s="3" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="28.5">
       <c r="A11" s="3" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="28.5">
       <c r="A12" s="3" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="28.5">
       <c r="A13" s="3" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="28.5">
       <c r="A14" s="3" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="3" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="3" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="3" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="3" t="s">
-        <v>1190</v>
+        <v>1179</v>
       </c>
     </row>
   </sheetData>
@@ -14866,57 +14943,57 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="28.5">
       <c r="A14" s="3" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="28.5">
       <c r="A15" s="3" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="28.5">
       <c r="A16" s="3" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="28.5">
       <c r="A17" s="3" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="28.5">
       <c r="A18" s="3" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="28.5">
       <c r="A19" s="3" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="28.5">
       <c r="A20" s="3" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="3" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="3" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
     </row>
   </sheetData>
@@ -14994,192 +15071,192 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="3" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="3" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="3" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="3" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="3" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="3" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="3" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="3" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="3" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="3" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="3" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="3" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="3" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="3" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="3" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="3" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="3" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="3" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="3" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="3" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="3" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="3" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="3" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="3" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="3" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="3" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="3" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="3" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="3" t="s">
-        <v>1111</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="3" t="s">
-        <v>1121</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="3" t="s">
-        <v>1170</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="3" t="s">
-        <v>1179</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="3" t="s">
-        <v>1190</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="3" t="s">
-        <v>1199</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="3" t="s">
-        <v>1214</v>
+        <v>1203</v>
       </c>
     </row>
   </sheetData>
@@ -15202,27 +15279,27 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
     </row>
   </sheetData>
@@ -15245,22 +15322,22 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
     </row>
   </sheetData>
@@ -15283,22 +15360,22 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
     </row>
   </sheetData>
